--- a/public/modele_creation.xlsx
+++ b/public/modele_creation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="28">
   <si>
     <t>Key</t>
   </si>
@@ -30,10 +30,7 @@
     <t/>
   </si>
   <si>
-    <t>Entreprise</t>
-  </si>
-  <si>
-    <t>Numero_Enregistrement</t>
+    <t>Organisation</t>
   </si>
   <si>
     <t>Secteur</t>
@@ -524,7 +521,7 @@
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15.6" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="43.09765625" style="1" customWidth="1"/>
@@ -600,7 +597,7 @@
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="3" t="s">
         <v>3</v>
       </c>
     </row>
@@ -616,15 +613,7 @@
       <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -650,39 +639,39 @@
         <v>2</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -700,31 +689,31 @@
   <sheetData>
     <row r="1" ht="16.2" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>15</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/public/modele_creation.xlsx
+++ b/public/modele_creation.xlsx
@@ -1,154 +1,61 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
-  <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="164011" filterPrivacy="true"/>
   <sheets>
-    <sheet sheetId="1" name="Configuration" state="visible" r:id="rId4"/>
-    <sheet sheetId="5" name="Parametres" state="veryHidden" r:id="rId5"/>
-    <sheet sheetId="2" name="Colleges" state="visible" r:id="rId6"/>
+    <sheet name="Configuration" sheetId="1" r:id="rId1"/>
+    <sheet name="Parametres" sheetId="2" r:id="rId2" state="veryHidden"/>
+    <sheet name="Colleges" sheetId="3" r:id="rId3"/>
+    <sheet name="Etablissements" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="28">
-  <si>
-    <t>Key</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Intitule</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Organisation</t>
-  </si>
-  <si>
-    <t>Secteur</t>
-  </si>
-  <si>
-    <t>Tutelle</t>
-  </si>
-  <si>
-    <t>Nom_RH</t>
-  </si>
-  <si>
-    <t>Telephone_RH</t>
-  </si>
-  <si>
-    <t>Email_RH</t>
-  </si>
-  <si>
-    <t>Date_scrutin</t>
-  </si>
-  <si>
-    <t>Affichage_listes</t>
-  </si>
-  <si>
-    <t>Possible_2nd_tour</t>
-  </si>
-  <si>
-    <t>2nd_tour</t>
-  </si>
-  <si>
-    <t>Privé</t>
-  </si>
-  <si>
-    <t>Oui</t>
-  </si>
-  <si>
-    <t>Parapublic</t>
-  </si>
-  <si>
-    <t>Non</t>
-  </si>
-  <si>
-    <t>Public</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Encadrement</t>
-  </si>
-  <si>
-    <t>encadrement</t>
-  </si>
-  <si>
-    <t>Cadre</t>
-  </si>
-  <si>
-    <t>cadre</t>
-  </si>
-  <si>
-    <t>Maîtrise</t>
-  </si>
-  <si>
-    <t>maitrise</t>
-  </si>
-  <si>
-    <t>Exécution</t>
-  </si>
-  <si>
-    <t>execution</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
+      <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <family val="1"/>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.0499893185216834"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -156,43 +63,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -517,206 +399,523 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor rgb="FF0070C0"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15.6" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="43.09765625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="31.59765625" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="11.19921875" style="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>3</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Key</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Value</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Intitule</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Organisation</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Secteur</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Tutelle</v>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Nom_RH</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Telephone_RH</v>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Email_RH</v>
+      </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Date_scrutin</v>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Affichage_listes</v>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Possible_2nd_tour</v>
+      </c>
+      <c r="B11" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B11"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor rgb="FF0070C0"/>
-  </sheetPr>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15.6" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="13.8984375" style="1" customWidth="1"/>
-    <col min="2" max="16384" width="11.19921875" style="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B4"/>
   <sheetData>
-    <row r="1" ht="16.2" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>27</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Secteur</v>
+      </c>
+      <c r="B1" t="str">
+        <v>2nd_tour</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Privé</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Oui</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Parapublic</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Non</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Public</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B4"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15.6" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
-  <cols>
-    <col min="1" max="16384" width="11.19921875" style="4" customWidth="1"/>
-  </cols>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B5"/>
   <sheetData>
-    <row r="1" ht="16.2" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>18</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Intitule</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Code</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Encadrement</v>
+      </c>
+      <c r="B2" t="str">
+        <v>encadrement</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Cadre</v>
+      </c>
+      <c r="B3" t="str">
+        <v>cadre</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Maîtrise</v>
+      </c>
+      <c r="B4" t="str">
+        <v>maitrise</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Exécution</v>
+      </c>
+      <c r="B5" t="str">
+        <v>execution</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M16"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Region__Localisation</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Nom_Etablissement__Site</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Responsable_Etablissement</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Contact_Telephone</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Lieu_vote</v>
+      </c>
+      <c r="F1" t="str">
+        <v>nb_sieges_Encadrement</v>
+      </c>
+      <c r="G1" t="str">
+        <v>nb_sieges_Cadre</v>
+      </c>
+      <c r="H1" t="str">
+        <v>nb_sieges_Maitrise</v>
+      </c>
+      <c r="I1" t="str">
+        <v>nb_sieges_Execution</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Nbre_electeurs_Encadrement</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Nbre_electeurs_Cadre</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Nbre _electeurs_Maitrise</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Nbre _electeurs_Execution</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>DRL</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Etablissement Exploitations Littoral</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Port-Gentil - Siège</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>DRN</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Etablissement Exploitations Ogooué-Ivindo</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Makokou - Siège</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>DRN</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Etablissement Exploitations Woleu-Ntem</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Oyem - Siège</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>DRCS</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Etablissement Exploitations Moyen-Ogooué</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Lambaréné - Siège</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>DRCS</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Etablissement Exploitations Ngounié</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Mouila - Siège</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>DRCS</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Etablissement Exploitations Nyanga et Excentrées</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Tchibanga - Siège</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>DRE</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Etablissement Exploitations Franceville et Excentrées</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Franceville - Siège</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>DRE</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Etablissement Exploitations Moanda et Ogooué-Lolo</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Moanda - Siège</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>EST.</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Etablissement Exploitations Ntoum et Vallée Mbè</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Ntoum - Siège</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>EST.</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Etablissement Exploitations Owendo-Damas</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Centre des métiers Jean Violas - Owendo</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>EST.</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Etablissement Nouveau Siège</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Libreville - Siège Social</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>EST.</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Etablissement Ancien Siège - Serena Mall</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Libreville -Ancien Siège</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>EST.</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Etablissement Base-Technique</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Libreville -Base-Technique</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>EST.</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Etablissement Peyrie</v>
+      </c>
+      <c r="E15" t="str">
+        <v>La Peyrie</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>EST.</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Etablissement Exploitations Nord</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Nzeng-Ayong</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:M16"/>
+  </ignoredErrors>
 </worksheet>
 </file>